--- a/jogos_2024-12-23.xlsx
+++ b/jogos_2024-12-23.xlsx
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="U8" t="n">
         <v>1.36</v>
       </c>
-      <c r="M8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="V8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.83</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['2', '81', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45649.58333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['34', '36']</t>
+          <t>['12', '67']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.88</v>
+        <v>1.42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>3.56</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45649.58333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['2', '45+8']</t>
+          <t>['2', '81', '83']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45649.58333333334</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -1863,22 +1863,22 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
         <v>1.83</v>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '71']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['34', '36']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45649.58333333334</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.95</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.28</v>
       </c>
-      <c r="X15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AC15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>['2', '45+8']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['12', '67']</t>
-        </is>
-      </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.56</v>
+        <v>2.66</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45649.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CSM Iaşi</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.67</v>
+        <v>6.25</v>
       </c>
       <c r="O17" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['44', '76']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45649.625</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>CSM Iaşi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.33</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['44', '76']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.83</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.29</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45649.625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.27</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>1.29</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="Y21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['5', '28', '90+1']</t>
+          <t>['22', '25', '35', '63', '90+6']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.67</v>
+        <v>4.33</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45649.66666666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="AD22" t="n">
         <v>2.5</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['22', '25', '35', '63', '90+6']</t>
+          <t>['5', '28', '90+1']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45649.66666666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="Q24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.22</v>
       </c>
-      <c r="M24" t="n">
-        <v>6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>11</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['48', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.33</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45649.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['48', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH25" t="n">
         <v>4.33</v>
       </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI25" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45649.69791666666</v>
